--- a/data/trans_orig/IP04D$notiene-Edad-trans_orig.xlsx
+++ b/data/trans_orig/IP04D$notiene-Edad-trans_orig.xlsx
@@ -732,12 +732,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>3648</t>
+          <t>3560</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>12167</t>
+          <t>11923</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -747,12 +747,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2,53%</t>
+          <t>2,46%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>8,42%</t>
+          <t>8,25%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -767,12 +767,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>2941</t>
+          <t>2851</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>12031</t>
+          <t>12777</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -782,12 +782,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>2,02%</t>
+          <t>1,96%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>8,28%</t>
+          <t>8,79%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>8289</t>
+          <t>8533</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>20552</t>
+          <t>21198</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>2,86%</t>
+          <t>2,94%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>7,09%</t>
+          <t>7,31%</t>
         </is>
       </c>
     </row>
@@ -845,12 +845,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>132286</t>
+          <t>132530</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>140805</t>
+          <t>140893</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -860,12 +860,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>91,58%</t>
+          <t>91,75%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>97,47%</t>
+          <t>97,54%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -880,12 +880,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>133331</t>
+          <t>132585</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>142421</t>
+          <t>142511</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -895,12 +895,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>91,72%</t>
+          <t>91,21%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>97,98%</t>
+          <t>98,04%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>269262</t>
+          <t>268616</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>281525</t>
+          <t>281281</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>92,91%</t>
+          <t>92,69%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>97,14%</t>
+          <t>97,06%</t>
         </is>
       </c>
     </row>
@@ -1075,12 +1075,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>4040</t>
+          <t>4470</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>13353</t>
+          <t>13696</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1090,12 +1090,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,71%</t>
+          <t>1,89%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>5,65%</t>
+          <t>5,8%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1110,12 +1110,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>5336</t>
+          <t>5261</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>16191</t>
+          <t>16076</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1125,12 +1125,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,99%</t>
+          <t>1,96%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>6,03%</t>
+          <t>5,99%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1145,12 +1145,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>11553</t>
+          <t>11987</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>25573</t>
+          <t>26334</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1160,12 +1160,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>2,29%</t>
+          <t>2,38%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>5,07%</t>
+          <t>5,22%</t>
         </is>
       </c>
     </row>
@@ -1188,12 +1188,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>222897</t>
+          <t>222554</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>232210</t>
+          <t>231780</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1203,12 +1203,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>94,35%</t>
+          <t>94,2%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>98,29%</t>
+          <t>98,11%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1223,12 +1223,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>252146</t>
+          <t>252261</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>263001</t>
+          <t>263076</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1238,12 +1238,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>93,97%</t>
+          <t>94,01%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>98,01%</t>
+          <t>98,04%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1258,12 +1258,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>479014</t>
+          <t>478253</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>493034</t>
+          <t>492600</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1273,12 +1273,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>94,93%</t>
+          <t>94,78%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>97,71%</t>
+          <t>97,62%</t>
         </is>
       </c>
     </row>
@@ -1418,12 +1418,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>2096</t>
+          <t>2098</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>9881</t>
+          <t>9561</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1438,7 +1438,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>6,32%</t>
+          <t>6,12%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1453,12 +1453,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>4017</t>
+          <t>4071</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>13436</t>
+          <t>14251</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1468,12 +1468,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>2,53%</t>
+          <t>2,57%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>8,47%</t>
+          <t>8,99%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>7638</t>
+          <t>7899</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>19795</t>
+          <t>20838</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1503,12 +1503,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,43%</t>
+          <t>2,51%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>6,29%</t>
+          <t>6,62%</t>
         </is>
       </c>
     </row>
@@ -1531,12 +1531,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>146372</t>
+          <t>146692</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>154157</t>
+          <t>154155</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1546,7 +1546,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>93,68%</t>
+          <t>93,88%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1566,12 +1566,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>145135</t>
+          <t>144320</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>154554</t>
+          <t>154500</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1581,12 +1581,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>91,53%</t>
+          <t>91,01%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>97,47%</t>
+          <t>97,43%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1601,12 +1601,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>295029</t>
+          <t>293986</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>307186</t>
+          <t>306925</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1616,12 +1616,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>93,71%</t>
+          <t>93,38%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>97,57%</t>
+          <t>97,49%</t>
         </is>
       </c>
     </row>
@@ -1761,12 +1761,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>4723</t>
+          <t>5303</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>14691</t>
+          <t>14754</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1776,12 +1776,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,76%</t>
+          <t>3,1%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>8,57%</t>
+          <t>8,61%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1796,12 +1796,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>2932</t>
+          <t>3060</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>11229</t>
+          <t>11914</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1811,12 +1811,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,63%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>6,24%</t>
+          <t>6,62%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1831,12 +1831,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>9673</t>
+          <t>10165</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>22203</t>
+          <t>23633</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1846,12 +1846,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>2,75%</t>
+          <t>2,89%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>6,32%</t>
+          <t>6,73%</t>
         </is>
       </c>
     </row>
@@ -1874,12 +1874,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>156646</t>
+          <t>156583</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>166614</t>
+          <t>166034</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1889,12 +1889,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>91,43%</t>
+          <t>91,39%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>97,24%</t>
+          <t>96,9%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1909,12 +1909,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>168726</t>
+          <t>168041</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>177023</t>
+          <t>176895</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1924,12 +1924,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>93,76%</t>
+          <t>93,38%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>98,37%</t>
+          <t>98,3%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1944,12 +1944,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>329089</t>
+          <t>327659</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>341619</t>
+          <t>341127</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1959,12 +1959,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>93,68%</t>
+          <t>93,27%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>97,25%</t>
+          <t>97,11%</t>
         </is>
       </c>
     </row>
@@ -2104,12 +2104,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>21329</t>
+          <t>20748</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>39146</t>
+          <t>37967</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2119,12 +2119,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>3,01%</t>
+          <t>2,93%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>5,53%</t>
+          <t>5,36%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2139,12 +2139,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>22306</t>
+          <t>22184</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>41019</t>
+          <t>42082</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2154,12 +2154,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>2,97%</t>
+          <t>2,95%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>5,45%</t>
+          <t>5,59%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2174,12 +2174,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>47894</t>
+          <t>47059</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>74764</t>
+          <t>72732</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2189,12 +2189,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>3,28%</t>
+          <t>3,22%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>5,12%</t>
+          <t>4,98%</t>
         </is>
       </c>
     </row>
@@ -2217,12 +2217,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>669146</t>
+          <t>670325</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>686963</t>
+          <t>687544</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2232,12 +2232,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>94,47%</t>
+          <t>94,64%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>96,99%</t>
+          <t>97,07%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2252,12 +2252,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>711206</t>
+          <t>710143</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>729919</t>
+          <t>730041</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2267,12 +2267,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>94,55%</t>
+          <t>94,41%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>97,03%</t>
+          <t>97,05%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2287,12 +2287,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1385753</t>
+          <t>1387785</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1412623</t>
+          <t>1413458</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2302,12 +2302,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>94,88%</t>
+          <t>95,02%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>96,72%</t>
+          <t>96,78%</t>
         </is>
       </c>
     </row>
@@ -2679,12 +2679,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>12266</t>
+          <t>13137</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>24833</t>
+          <t>25087</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2694,12 +2694,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>9,32%</t>
+          <t>9,98%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>18,86%</t>
+          <t>19,06%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2714,12 +2714,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>12084</t>
+          <t>12201</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>25183</t>
+          <t>24623</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2729,12 +2729,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>9,73%</t>
+          <t>9,83%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>20,28%</t>
+          <t>19,83%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2749,12 +2749,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>28154</t>
+          <t>28322</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>45310</t>
+          <t>46439</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2764,12 +2764,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>11,01%</t>
+          <t>11,07%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>17,71%</t>
+          <t>18,15%</t>
         </is>
       </c>
     </row>
@@ -2792,12 +2792,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>106821</t>
+          <t>106567</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>119388</t>
+          <t>118517</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2807,12 +2807,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>81,14%</t>
+          <t>80,94%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>90,68%</t>
+          <t>90,02%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2827,12 +2827,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>98981</t>
+          <t>99541</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>112080</t>
+          <t>111963</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2842,12 +2842,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>79,72%</t>
+          <t>80,17%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>90,27%</t>
+          <t>90,17%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2862,12 +2862,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>210508</t>
+          <t>209379</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>227664</t>
+          <t>227496</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2877,12 +2877,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>82,29%</t>
+          <t>81,85%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>88,99%</t>
+          <t>88,93%</t>
         </is>
       </c>
     </row>
@@ -3022,12 +3022,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>17748</t>
+          <t>17628</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>32218</t>
+          <t>32254</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3037,12 +3037,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>8,51%</t>
+          <t>8,46%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>15,46%</t>
+          <t>15,47%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3057,12 +3057,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>29118</t>
+          <t>28752</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>46579</t>
+          <t>47379</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3072,12 +3072,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>11,37%</t>
+          <t>11,23%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>18,19%</t>
+          <t>18,5%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3092,12 +3092,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>50460</t>
+          <t>49469</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>73543</t>
+          <t>73070</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3107,12 +3107,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>10,86%</t>
+          <t>10,65%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>15,83%</t>
+          <t>15,73%</t>
         </is>
       </c>
     </row>
@@ -3135,12 +3135,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>176230</t>
+          <t>176194</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>190700</t>
+          <t>190820</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3150,12 +3150,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>84,54%</t>
+          <t>84,53%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>91,49%</t>
+          <t>91,54%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3170,12 +3170,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>209505</t>
+          <t>208705</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>226966</t>
+          <t>227332</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3185,12 +3185,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>81,81%</t>
+          <t>81,5%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>88,63%</t>
+          <t>88,77%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3205,12 +3205,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>390989</t>
+          <t>391462</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>414072</t>
+          <t>415063</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3220,12 +3220,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>84,17%</t>
+          <t>84,27%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>89,14%</t>
+          <t>89,35%</t>
         </is>
       </c>
     </row>
@@ -3365,12 +3365,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>18719</t>
+          <t>18272</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>33351</t>
+          <t>34142</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3380,12 +3380,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>9,99%</t>
+          <t>9,75%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>17,79%</t>
+          <t>18,22%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3400,12 +3400,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>24153</t>
+          <t>23937</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>41239</t>
+          <t>41126</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3415,12 +3415,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>12,96%</t>
+          <t>12,84%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>22,13%</t>
+          <t>22,06%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3435,12 +3435,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>45995</t>
+          <t>45670</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>68827</t>
+          <t>69467</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3450,12 +3450,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>12,3%</t>
+          <t>12,22%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>18,41%</t>
+          <t>18,58%</t>
         </is>
       </c>
     </row>
@@ -3478,12 +3478,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>154089</t>
+          <t>153298</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>168721</t>
+          <t>169168</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3493,12 +3493,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>82,21%</t>
+          <t>81,78%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>90,01%</t>
+          <t>90,25%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3513,12 +3513,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>145148</t>
+          <t>145261</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>162234</t>
+          <t>162450</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3528,12 +3528,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>77,87%</t>
+          <t>77,94%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>87,04%</t>
+          <t>87,16%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3548,12 +3548,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>305000</t>
+          <t>304360</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>327832</t>
+          <t>328157</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3563,12 +3563,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>81,59%</t>
+          <t>81,42%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>87,7%</t>
+          <t>87,78%</t>
         </is>
       </c>
     </row>
@@ -3708,12 +3708,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>17435</t>
+          <t>17418</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>32889</t>
+          <t>32638</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3723,12 +3723,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>10,1%</t>
+          <t>10,09%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>19,05%</t>
+          <t>18,91%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3743,12 +3743,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>16828</t>
+          <t>17388</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>32881</t>
+          <t>33204</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3758,12 +3758,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>9,71%</t>
+          <t>10,03%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>18,97%</t>
+          <t>19,15%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3778,12 +3778,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>39801</t>
+          <t>38744</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>62536</t>
+          <t>60279</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3793,12 +3793,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>11,5%</t>
+          <t>11,2%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>18,07%</t>
+          <t>17,42%</t>
         </is>
       </c>
     </row>
@@ -3821,12 +3821,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>139749</t>
+          <t>140000</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>155203</t>
+          <t>155220</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3836,12 +3836,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>80,95%</t>
+          <t>81,09%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>89,9%</t>
+          <t>89,91%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3856,12 +3856,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>140496</t>
+          <t>140173</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>156549</t>
+          <t>155989</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3871,12 +3871,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>81,03%</t>
+          <t>80,85%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>90,29%</t>
+          <t>89,97%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3891,12 +3891,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>283479</t>
+          <t>285736</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>306214</t>
+          <t>307271</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3906,12 +3906,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>81,93%</t>
+          <t>82,58%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>88,5%</t>
+          <t>88,8%</t>
         </is>
       </c>
     </row>
@@ -4051,12 +4051,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>78140</t>
+          <t>79563</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>107958</t>
+          <t>105936</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4066,12 +4066,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>11,16%</t>
+          <t>11,36%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>15,42%</t>
+          <t>15,13%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4086,12 +4086,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>95798</t>
+          <t>96101</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>131128</t>
+          <t>128502</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4101,12 +4101,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>12,95%</t>
+          <t>12,99%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>17,72%</t>
+          <t>17,36%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4121,12 +4121,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>182313</t>
+          <t>181435</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>228599</t>
+          <t>227202</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4136,12 +4136,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>12,66%</t>
+          <t>12,6%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>15,87%</t>
+          <t>15,78%</t>
         </is>
       </c>
     </row>
@@ -4164,12 +4164,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>592223</t>
+          <t>594245</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>622041</t>
+          <t>620618</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4179,12 +4179,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>84,58%</t>
+          <t>84,87%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>88,84%</t>
+          <t>88,64%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4199,12 +4199,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>608883</t>
+          <t>611509</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>644213</t>
+          <t>643910</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4214,12 +4214,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>82,28%</t>
+          <t>82,64%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>87,05%</t>
+          <t>87,01%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4234,12 +4234,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1211593</t>
+          <t>1212990</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1257879</t>
+          <t>1258757</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4249,12 +4249,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>84,13%</t>
+          <t>84,22%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>87,34%</t>
+          <t>87,4%</t>
         </is>
       </c>
     </row>
@@ -4626,12 +4626,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>6450</t>
+          <t>6318</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>16000</t>
+          <t>15647</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4641,12 +4641,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>11,21%</t>
+          <t>10,99%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>27,82%</t>
+          <t>27,21%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4661,12 +4661,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>2146</t>
+          <t>2361</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>8507</t>
+          <t>8867</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4676,12 +4676,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>3,49%</t>
+          <t>3,84%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>13,85%</t>
+          <t>14,43%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4696,12 +4696,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>9788</t>
+          <t>9502</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>21716</t>
+          <t>21153</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4711,12 +4711,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>8,23%</t>
+          <t>7,99%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>18,26%</t>
+          <t>17,78%</t>
         </is>
       </c>
     </row>
@@ -4739,12 +4739,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>41511</t>
+          <t>41864</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>51061</t>
+          <t>51193</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4754,12 +4754,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>72,18%</t>
+          <t>72,79%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>88,79%</t>
+          <t>89,01%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4774,12 +4774,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>52937</t>
+          <t>52577</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>59298</t>
+          <t>59083</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4789,12 +4789,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>86,15%</t>
+          <t>85,57%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>96,51%</t>
+          <t>96,16%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4809,12 +4809,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>97239</t>
+          <t>97802</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>109167</t>
+          <t>109453</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4824,12 +4824,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>81,74%</t>
+          <t>82,22%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>91,77%</t>
+          <t>92,01%</t>
         </is>
       </c>
     </row>
@@ -4974,7 +4974,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>32072</t>
+          <t>33054</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4989,7 +4989,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>20,13%</t>
+          <t>20,75%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5004,12 +5004,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>13519</t>
+          <t>14017</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>28746</t>
+          <t>28548</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5019,12 +5019,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>7,43%</t>
+          <t>7,71%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>15,81%</t>
+          <t>15,7%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5039,12 +5039,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>33652</t>
+          <t>32557</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>56273</t>
+          <t>55625</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5054,12 +5054,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>9,86%</t>
+          <t>9,54%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>16,5%</t>
+          <t>16,31%</t>
         </is>
       </c>
     </row>
@@ -5082,7 +5082,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>127227</t>
+          <t>126245</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -5097,7 +5097,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>79,87%</t>
+          <t>79,25%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -5117,12 +5117,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>153101</t>
+          <t>153299</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>168328</t>
+          <t>167830</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -5132,12 +5132,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>84,19%</t>
+          <t>84,3%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>92,57%</t>
+          <t>92,29%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5152,12 +5152,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>284874</t>
+          <t>285522</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>307495</t>
+          <t>308590</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5167,12 +5167,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>83,5%</t>
+          <t>83,69%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>90,14%</t>
+          <t>90,46%</t>
         </is>
       </c>
     </row>
@@ -5312,12 +5312,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>12838</t>
+          <t>12695</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>26331</t>
+          <t>26912</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5327,12 +5327,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>7,38%</t>
+          <t>7,3%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>15,14%</t>
+          <t>15,48%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5347,12 +5347,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>27485</t>
+          <t>28758</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>51359</t>
+          <t>54100</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5362,12 +5362,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>12,99%</t>
+          <t>13,59%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>24,28%</t>
+          <t>25,57%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5382,12 +5382,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>45083</t>
+          <t>44651</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>74410</t>
+          <t>73663</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5397,12 +5397,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>11,7%</t>
+          <t>11,58%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>19,31%</t>
+          <t>19,11%</t>
         </is>
       </c>
     </row>
@@ -5425,12 +5425,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>147557</t>
+          <t>146976</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>161050</t>
+          <t>161193</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -5440,12 +5440,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>84,86%</t>
+          <t>84,52%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>92,62%</t>
+          <t>92,7%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -5460,12 +5460,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>160188</t>
+          <t>157447</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>184062</t>
+          <t>182789</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -5475,12 +5475,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>75,72%</t>
+          <t>74,43%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>87,01%</t>
+          <t>86,41%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5495,12 +5495,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>311024</t>
+          <t>311771</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>340351</t>
+          <t>340783</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5510,12 +5510,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>80,69%</t>
+          <t>80,89%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>88,3%</t>
+          <t>88,42%</t>
         </is>
       </c>
     </row>
@@ -5655,12 +5655,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>25012</t>
+          <t>24532</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>57545</t>
+          <t>55813</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5670,12 +5670,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>9,11%</t>
+          <t>8,94%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>20,97%</t>
+          <t>20,34%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5690,12 +5690,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>29350</t>
+          <t>29661</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>60776</t>
+          <t>60473</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5705,12 +5705,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>9,61%</t>
+          <t>9,71%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>19,9%</t>
+          <t>19,8%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5725,12 +5725,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>60855</t>
+          <t>60408</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>106809</t>
+          <t>106410</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5740,12 +5740,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>10,49%</t>
+          <t>10,42%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>18,42%</t>
+          <t>18,35%</t>
         </is>
       </c>
     </row>
@@ -5768,12 +5768,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>216913</t>
+          <t>218645</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>249446</t>
+          <t>249926</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5783,12 +5783,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>79,03%</t>
+          <t>79,66%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>90,89%</t>
+          <t>91,06%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5803,12 +5803,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>244707</t>
+          <t>245010</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>276133</t>
+          <t>275822</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5818,12 +5818,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>80,1%</t>
+          <t>80,2%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>90,39%</t>
+          <t>90,29%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5838,12 +5838,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>473132</t>
+          <t>473531</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>519086</t>
+          <t>519533</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5853,12 +5853,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>81,58%</t>
+          <t>81,65%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>89,51%</t>
+          <t>89,58%</t>
         </is>
       </c>
     </row>
@@ -5998,12 +5998,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>72945</t>
+          <t>71831</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>110824</t>
+          <t>111837</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -6013,12 +6013,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>10,97%</t>
+          <t>10,8%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>16,66%</t>
+          <t>16,81%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6033,12 +6033,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>86163</t>
+          <t>85913</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>130400</t>
+          <t>128326</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6048,12 +6048,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>11,33%</t>
+          <t>11,3%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>17,15%</t>
+          <t>16,88%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6068,12 +6068,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>168093</t>
+          <t>168616</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>229820</t>
+          <t>228630</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6083,12 +6083,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>11,79%</t>
+          <t>11,83%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>16,12%</t>
+          <t>16,04%</t>
         </is>
       </c>
     </row>
@@ -6111,12 +6111,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>554332</t>
+          <t>553319</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>592211</t>
+          <t>593325</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6126,12 +6126,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>83,34%</t>
+          <t>83,19%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>89,03%</t>
+          <t>89,2%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -6146,12 +6146,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>629922</t>
+          <t>631996</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>674159</t>
+          <t>674409</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6161,12 +6161,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>82,85%</t>
+          <t>83,12%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>88,67%</t>
+          <t>88,7%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6181,12 +6181,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1195657</t>
+          <t>1196847</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1257384</t>
+          <t>1256861</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6196,12 +6196,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>83,88%</t>
+          <t>83,96%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>88,21%</t>
+          <t>88,17%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IP04D$notiene-Edad-trans_orig.xlsx
+++ b/data/trans_orig/IP04D$notiene-Edad-trans_orig.xlsx
@@ -543,7 +543,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -554,7 +554,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -722,72 +722,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>6676</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>2975</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>12895</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>4,59%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>2,05%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>8,87%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>10</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>6871</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>3560</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>11923</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>3620</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>12498</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>4,76%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>2,46%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>8,25%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>6676</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>2851</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>12777</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>4,59%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,96%</t>
+          <t>2,51%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>8,79%</t>
+          <t>8,65%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>8533</t>
+          <t>8088</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>21198</t>
+          <t>20890</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>2,94%</t>
+          <t>2,79%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>7,31%</t>
+          <t>7,21%</t>
         </is>
       </c>
     </row>
@@ -835,72 +835,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>198</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>138686</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>132467</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>142387</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>95,41%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>91,13%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>97,95%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>206</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>137582</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>132530</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>140893</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>131955</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>140833</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>95,24%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>91,75%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>97,54%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>198</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>138686</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>132585</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>142511</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>95,41%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>91,21%</t>
+          <t>91,35%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>98,04%</t>
+          <t>97,49%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>268616</t>
+          <t>268924</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>281281</t>
+          <t>281726</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>92,69%</t>
+          <t>92,79%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>97,06%</t>
+          <t>97,21%</t>
         </is>
       </c>
     </row>
@@ -948,57 +948,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>206</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>145362</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>145362</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>145362</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>216</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>144453</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>144453</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>144453</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>206</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>145362</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>145362</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>145362</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1065,72 +1065,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>9670</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>5505</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>17396</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>3,6%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>2,05%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>6,48%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>11</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>8051</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>4470</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>13696</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>4010</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>13533</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>3,41%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>1,89%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>5,8%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>9670</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>5261</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>16076</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>3,6%</t>
-        </is>
-      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,96%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>5,99%</t>
+          <t>5,73%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1145,12 +1145,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>11987</t>
+          <t>12051</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>26334</t>
+          <t>26370</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1160,12 +1160,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>2,38%</t>
+          <t>2,39%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>5,22%</t>
+          <t>5,23%</t>
         </is>
       </c>
     </row>
@@ -1178,72 +1178,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>360</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>258667</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>250941</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>262832</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>96,4%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>93,52%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>97,95%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>329</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>228199</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>222554</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>231780</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>222717</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>232240</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>96,59%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>94,2%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>98,11%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>360</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>258667</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>252261</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>263076</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>96,4%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>94,01%</t>
+          <t>94,27%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>98,04%</t>
+          <t>98,3%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1258,12 +1258,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>478253</t>
+          <t>478217</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>492600</t>
+          <t>492536</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1273,12 +1273,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>94,78%</t>
+          <t>94,77%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>97,62%</t>
+          <t>97,61%</t>
         </is>
       </c>
     </row>
@@ -1291,57 +1291,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>373</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>268337</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>268337</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>268337</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>340</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>236250</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>236250</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>236250</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>373</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>268337</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>268337</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>268337</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1408,72 +1408,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>7856</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>3835</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>13952</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>4,95%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>2,42%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>8,8%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>4938</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>2098</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>9561</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>2168</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>10228</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>3,16%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>1,34%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>6,12%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>7856</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>4071</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>14251</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>4,95%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>2,57%</t>
+          <t>1,39%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>8,99%</t>
+          <t>6,55%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>7899</t>
+          <t>7569</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>20838</t>
+          <t>20074</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1503,12 +1503,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,51%</t>
+          <t>2,4%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>6,62%</t>
+          <t>6,38%</t>
         </is>
       </c>
     </row>
@@ -1521,72 +1521,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>218</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>150715</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>144619</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>154736</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>95,05%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>91,2%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>97,58%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>215</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>151315</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>146692</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>154155</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>146025</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>154085</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>96,84%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>93,88%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>98,66%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>218</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>150715</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>144320</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>154500</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>95,05%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>91,01%</t>
+          <t>93,45%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>97,43%</t>
+          <t>98,61%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1601,12 +1601,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>293986</t>
+          <t>294750</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>306925</t>
+          <t>307255</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1616,12 +1616,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>93,38%</t>
+          <t>93,62%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>97,49%</t>
+          <t>97,6%</t>
         </is>
       </c>
     </row>
@@ -1634,57 +1634,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>228</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>158571</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>158571</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>158571</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>222</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>156253</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>156253</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>156253</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>228</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>158571</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>158571</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>158571</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1751,72 +1751,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>6335</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>3262</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>11920</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>3,52%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>1,81%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>6,62%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>13</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>9062</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>5303</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>14754</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>4791</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>15317</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>5,29%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>3,1%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>8,61%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>6335</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>3060</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>11914</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>3,52%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>2,8%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>6,62%</t>
+          <t>8,94%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1831,12 +1831,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>10165</t>
+          <t>10303</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>23633</t>
+          <t>22822</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1846,12 +1846,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>2,89%</t>
+          <t>2,93%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>6,73%</t>
+          <t>6,5%</t>
         </is>
       </c>
     </row>
@@ -1864,72 +1864,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>256</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>173620</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>168035</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>176693</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>96,48%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>93,38%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>98,19%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>230</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>162275</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>156583</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>166034</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>156020</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>166546</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>94,71%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>91,39%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>96,9%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>256</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>173620</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>168041</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>176895</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>96,48%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>93,38%</t>
+          <t>91,06%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>98,3%</t>
+          <t>97,2%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1944,12 +1944,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>327659</t>
+          <t>328470</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>341127</t>
+          <t>340989</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1959,12 +1959,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>93,27%</t>
+          <t>93,5%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>97,11%</t>
+          <t>97,07%</t>
         </is>
       </c>
     </row>
@@ -1977,57 +1977,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>265</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>179955</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>179955</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>179955</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>243</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>171337</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>171337</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>171337</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>265</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>179955</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>179955</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>179955</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2094,72 +2094,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>30537</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>22281</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>41389</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>4,06%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>2,96%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>5,5%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>41</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>28922</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>20748</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>37967</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>21305</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>39198</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>4,08%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>2,93%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>5,36%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>30537</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>22184</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>42082</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>4,06%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>2,95%</t>
+          <t>3,01%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>5,59%</t>
+          <t>5,53%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2174,12 +2174,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>47059</t>
+          <t>47920</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>72732</t>
+          <t>73045</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2189,12 +2189,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>3,22%</t>
+          <t>3,28%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>4,98%</t>
+          <t>5,0%</t>
         </is>
       </c>
     </row>
@@ -2207,72 +2207,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>1032</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>721688</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>710836</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>729944</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>95,94%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>94,5%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>97,04%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>980</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>679370</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>670325</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>687544</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>669094</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>686987</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>95,92%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>94,64%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>97,07%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>1032</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>721688</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>710143</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>730041</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>95,94%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>94,41%</t>
+          <t>94,47%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>97,05%</t>
+          <t>96,99%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2287,12 +2287,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1387785</t>
+          <t>1387472</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1413458</t>
+          <t>1412597</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2302,12 +2302,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>95,02%</t>
+          <t>95,0%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>96,78%</t>
+          <t>96,72%</t>
         </is>
       </c>
     </row>
@@ -2320,57 +2320,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>1072</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>752225</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>752225</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>752225</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>1021</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>708292</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>708292</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>708292</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>1072</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>752225</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>752225</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>752225</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2490,7 +2490,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -2501,7 +2501,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -2669,72 +2669,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>18012</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>12431</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>26261</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>14,51%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>10,01%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>21,15%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>30</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>18263</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>13137</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>25087</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>12446</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>24565</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>13,87%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>9,98%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>19,06%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>18012</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>12201</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>24623</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>14,51%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>9,83%</t>
+          <t>9,45%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>19,83%</t>
+          <t>18,66%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2749,12 +2749,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>28322</t>
+          <t>28109</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>46439</t>
+          <t>45731</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2764,12 +2764,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>11,07%</t>
+          <t>10,99%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>18,15%</t>
+          <t>17,88%</t>
         </is>
       </c>
     </row>
@@ -2782,72 +2782,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>160</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>106152</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>97903</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>111733</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>85,49%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>78,85%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>89,99%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>181</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>113391</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>106567</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>118517</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>107089</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>119208</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>86,13%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>80,94%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>90,02%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>160</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>106152</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>99541</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>111963</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>85,49%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>80,17%</t>
+          <t>81,34%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>90,17%</t>
+          <t>90,55%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2862,12 +2862,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>209379</t>
+          <t>210087</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>227496</t>
+          <t>227709</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2877,12 +2877,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>81,85%</t>
+          <t>82,12%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>88,93%</t>
+          <t>89,01%</t>
         </is>
       </c>
     </row>
@@ -2895,57 +2895,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>187</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>124164</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>124164</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>124164</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>211</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>131654</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>131654</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>131654</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>187</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>124164</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>124164</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>124164</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3012,72 +3012,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>53</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>37307</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>29057</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>47179</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>14,57%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>11,35%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>18,42%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>39</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>24034</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>17628</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>32254</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>17671</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>33177</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>11,53%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>8,46%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>15,47%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>53</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>37307</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>28752</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>47379</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>14,57%</t>
-        </is>
-      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>11,23%</t>
+          <t>8,48%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>18,5%</t>
+          <t>15,92%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3092,12 +3092,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>49469</t>
+          <t>50166</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>73070</t>
+          <t>73482</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3107,12 +3107,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>10,65%</t>
+          <t>10,8%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>15,73%</t>
+          <t>15,82%</t>
         </is>
       </c>
     </row>
@@ -3125,72 +3125,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>324</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>218777</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>208905</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>227027</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>85,43%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>81,58%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>88,65%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>290</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>184414</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>176194</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>190820</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>175271</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>190777</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>88,47%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>84,53%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>91,54%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>324</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>218777</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>208705</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>227332</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>85,43%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>81,5%</t>
+          <t>84,08%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>88,77%</t>
+          <t>91,52%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3205,12 +3205,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>391462</t>
+          <t>391050</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>415063</t>
+          <t>414366</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3220,12 +3220,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>84,27%</t>
+          <t>84,18%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>89,35%</t>
+          <t>89,2%</t>
         </is>
       </c>
     </row>
@@ -3238,57 +3238,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>377</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>256084</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>256084</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>256084</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>329</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>208448</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>208448</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>208448</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>377</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>256084</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>256084</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>256084</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -3355,72 +3355,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>31576</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>23557</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>41067</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>16,94%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>12,64%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>22,03%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>37</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>25190</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>18272</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>34142</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>18417</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>34010</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>13,44%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>9,75%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>18,22%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>43</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>31576</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>23937</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>41126</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>16,94%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>12,84%</t>
+          <t>9,83%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>22,06%</t>
+          <t>18,14%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3435,12 +3435,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>45670</t>
+          <t>46378</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>69467</t>
+          <t>68775</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3450,12 +3450,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>12,22%</t>
+          <t>12,41%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>18,58%</t>
+          <t>18,4%</t>
         </is>
       </c>
     </row>
@@ -3468,72 +3468,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>217</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>154811</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>145320</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>162830</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>83,06%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>77,97%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>87,36%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>233</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>162250</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>153298</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>169168</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>153430</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>169023</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>86,56%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>81,78%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>90,25%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>217</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>154811</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>145261</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>162450</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>83,06%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>77,94%</t>
+          <t>81,86%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>87,16%</t>
+          <t>90,17%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3548,12 +3548,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>304360</t>
+          <t>305052</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>328157</t>
+          <t>327449</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3563,12 +3563,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>81,42%</t>
+          <t>81,6%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>87,78%</t>
+          <t>87,59%</t>
         </is>
       </c>
     </row>
@@ -3581,57 +3581,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>260</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>186387</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>186387</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>186387</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>270</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>187440</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>187440</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>187440</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>260</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>186387</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>186387</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>186387</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -3698,72 +3698,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>24368</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>17143</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>33318</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>14,05%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>9,89%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>19,22%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>35</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>24498</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>17418</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>32638</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>17921</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>33091</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>14,19%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>10,09%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>18,91%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>32</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>24368</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>17388</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>33204</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>14,05%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>10,03%</t>
+          <t>10,38%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>19,15%</t>
+          <t>19,17%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3778,12 +3778,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>38744</t>
+          <t>38078</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>60279</t>
+          <t>61185</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3793,12 +3793,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>11,2%</t>
+          <t>11,0%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>17,42%</t>
+          <t>17,68%</t>
         </is>
       </c>
     </row>
@@ -3811,72 +3811,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>202</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>149009</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>140059</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>156234</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>85,95%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>80,78%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>90,11%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>210</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>148140</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>140000</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>155220</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>139547</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>154717</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>85,81%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>81,09%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>89,91%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>202</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>149009</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>140173</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>155989</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>85,95%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>80,85%</t>
+          <t>80,83%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>89,97%</t>
+          <t>89,62%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3891,12 +3891,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>285736</t>
+          <t>284830</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>307271</t>
+          <t>307937</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3906,12 +3906,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>82,58%</t>
+          <t>82,32%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>88,8%</t>
+          <t>89,0%</t>
         </is>
       </c>
     </row>
@@ -3924,57 +3924,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>234</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>173377</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>173377</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>173377</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>245</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>172638</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>172638</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>172638</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>234</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>173377</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>173377</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>173377</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -4041,72 +4041,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>155</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>111264</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>94773</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>129732</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>15,04%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>12,81%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>17,53%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>141</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>91985</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>79563</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>105936</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>78028</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>106883</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>13,14%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>11,36%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>15,13%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>155</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>111264</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>96101</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>128502</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>15,04%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>12,99%</t>
+          <t>11,14%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>17,36%</t>
+          <t>15,27%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4121,12 +4121,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>181435</t>
+          <t>180428</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>227202</t>
+          <t>225587</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4136,12 +4136,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>12,6%</t>
+          <t>12,53%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>15,78%</t>
+          <t>15,66%</t>
         </is>
       </c>
     </row>
@@ -4154,72 +4154,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>903</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>628747</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>610279</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>645238</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>84,96%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>82,47%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>87,19%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>914</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>608196</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>594245</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>620618</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>593298</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>622153</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>86,86%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>84,87%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>88,64%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>903</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>628747</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>611509</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>643910</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>84,96%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>82,64%</t>
+          <t>84,73%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>87,01%</t>
+          <t>88,86%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4234,12 +4234,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1212990</t>
+          <t>1214605</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1258757</t>
+          <t>1259764</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4249,12 +4249,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>84,22%</t>
+          <t>84,34%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>87,4%</t>
+          <t>87,47%</t>
         </is>
       </c>
     </row>
@@ -4267,57 +4267,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>1058</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>740011</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>740011</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>740011</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>1055</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>700181</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>700181</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>700181</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>1058</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>740011</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>740011</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>740011</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -4437,7 +4437,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -4448,7 +4448,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -4616,72 +4616,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>4462</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>2103</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>7935</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>8,83%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>4,16%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>15,7%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>16</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>10154</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>6318</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>15647</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>17,66%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>10,99%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>27,21%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>4645</t>
+          <t>9588</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>2361</t>
+          <t>5698</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>8867</t>
+          <t>14192</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>7,56%</t>
+          <t>18,41%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>3,84%</t>
+          <t>10,94%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>14,43%</t>
+          <t>27,24%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4691,32 +4691,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>14799</t>
+          <t>14051</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>9502</t>
+          <t>9385</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>21153</t>
+          <t>20659</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>12,44%</t>
+          <t>13,69%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>7,99%</t>
+          <t>9,14%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>17,78%</t>
+          <t>20,13%</t>
         </is>
       </c>
     </row>
@@ -4729,72 +4729,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>107</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>46075</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>42602</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>48434</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>91,17%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>84,3%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>95,84%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>93</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>47357</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>41864</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>51193</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>82,34%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>72,79%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>89,01%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>107</t>
-        </is>
-      </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>56799</t>
+          <t>42502</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>52577</t>
+          <t>37898</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>59083</t>
+          <t>46392</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>92,44%</t>
+          <t>81,59%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>85,57%</t>
+          <t>72,76%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>96,16%</t>
+          <t>89,06%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4804,32 +4804,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>104156</t>
+          <t>88576</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>97802</t>
+          <t>81968</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>109453</t>
+          <t>93242</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>87,56%</t>
+          <t>86,31%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>82,22%</t>
+          <t>79,87%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>92,01%</t>
+          <t>90,86%</t>
         </is>
       </c>
     </row>
@@ -4842,57 +4842,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>116</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>50537</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>50537</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>50537</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>109</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>57511</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>57511</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>57511</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>116</t>
-        </is>
-      </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>61444</t>
+          <t>52090</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>61444</t>
+          <t>52090</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>61444</t>
+          <t>52090</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4917,17 +4917,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>118955</t>
+          <t>102627</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>118955</t>
+          <t>102627</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>118955</t>
+          <t>102627</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4959,72 +4959,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>16647</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>11157</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>23652</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>10,61%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>7,11%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>15,07%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>33</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>22779</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>15589</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>33054</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>14,3%</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>9,79%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>20,75%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>29</t>
-        </is>
-      </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>20270</t>
+          <t>18586</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>14017</t>
+          <t>12340</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>28548</t>
+          <t>25261</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>11,15%</t>
+          <t>12,77%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>7,71%</t>
+          <t>8,48%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>15,7%</t>
+          <t>17,36%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5034,32 +5034,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>43049</t>
+          <t>35233</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>32557</t>
+          <t>27446</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>55625</t>
+          <t>46118</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>12,62%</t>
+          <t>11,65%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>9,54%</t>
+          <t>9,08%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>16,31%</t>
+          <t>15,25%</t>
         </is>
       </c>
     </row>
@@ -5072,72 +5072,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>246</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>140258</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>133253</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>145748</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>89,39%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>84,93%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>92,89%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>225</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>136520</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>126245</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>143710</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>85,7%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>79,25%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>90,21%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>246</t>
-        </is>
-      </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>161577</t>
+          <t>126932</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>153299</t>
+          <t>120257</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>167830</t>
+          <t>133178</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>88,85%</t>
+          <t>87,23%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>84,3%</t>
+          <t>82,64%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>92,29%</t>
+          <t>91,52%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5147,32 +5147,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>298098</t>
+          <t>267190</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>285522</t>
+          <t>256305</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>308590</t>
+          <t>274977</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>87,38%</t>
+          <t>88,35%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>83,69%</t>
+          <t>84,75%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>90,46%</t>
+          <t>90,92%</t>
         </is>
       </c>
     </row>
@@ -5185,57 +5185,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>275</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>156905</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>156905</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>156905</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>258</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>159299</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>159299</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>159299</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>275</t>
-        </is>
-      </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>181847</t>
+          <t>145518</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>181847</t>
+          <t>145518</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>181847</t>
+          <t>145518</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -5260,17 +5260,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>341147</t>
+          <t>302423</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>341147</t>
+          <t>302423</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>341147</t>
+          <t>302423</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -5302,72 +5302,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>32801</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>24753</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>44745</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>16,47%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>12,43%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>22,47%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>27</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>18631</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>12695</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>26912</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>10,71%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>7,3%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>15,48%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>39</t>
-        </is>
-      </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>38637</t>
+          <t>18818</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>28758</t>
+          <t>13179</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>54100</t>
+          <t>27217</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>18,26%</t>
+          <t>10,72%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>13,59%</t>
+          <t>7,51%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>25,57%</t>
+          <t>15,51%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5377,32 +5377,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>57268</t>
+          <t>51620</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>44651</t>
+          <t>40248</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>73663</t>
+          <t>63977</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>14,86%</t>
+          <t>13,78%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>11,58%</t>
+          <t>10,74%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>19,11%</t>
+          <t>17,07%</t>
         </is>
       </c>
     </row>
@@ -5415,72 +5415,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>203</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>166368</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>154424</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>174416</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>83,53%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>77,53%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>87,57%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>207</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>155257</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>146976</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>161193</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>89,29%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>84,52%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>92,7%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>203</t>
-        </is>
-      </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>172910</t>
+          <t>156700</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>157447</t>
+          <t>148301</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>182789</t>
+          <t>162339</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>81,74%</t>
+          <t>89,28%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>74,43%</t>
+          <t>84,49%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>86,41%</t>
+          <t>92,49%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5490,32 +5490,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>328166</t>
+          <t>323066</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>311771</t>
+          <t>310709</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>340783</t>
+          <t>334438</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>85,14%</t>
+          <t>86,22%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>80,89%</t>
+          <t>82,93%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>88,42%</t>
+          <t>89,26%</t>
         </is>
       </c>
     </row>
@@ -5528,57 +5528,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>242</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>199169</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>199169</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>199169</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>234</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>173888</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>173888</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>173888</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>242</t>
-        </is>
-      </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>211547</t>
+          <t>175518</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>211547</t>
+          <t>175518</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>211547</t>
+          <t>175518</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -5603,17 +5603,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>385434</t>
+          <t>374686</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>385434</t>
+          <t>374686</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>385434</t>
+          <t>374686</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -5645,72 +5645,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>33729</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>24280</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>45703</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>11,53%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>8,3%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>15,62%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>41</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>38129</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>24532</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>55813</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>13,89%</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>8,94%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>20,34%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>43</t>
-        </is>
-      </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>42003</t>
+          <t>29608</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>29661</t>
+          <t>20802</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>60473</t>
+          <t>38967</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>13,75%</t>
+          <t>11,59%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>9,71%</t>
+          <t>8,14%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>19,8%</t>
+          <t>15,25%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5720,32 +5720,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>80132</t>
+          <t>63336</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>60408</t>
+          <t>50662</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>106410</t>
+          <t>77732</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>13,82%</t>
+          <t>11,56%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>10,42%</t>
+          <t>9,24%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>18,35%</t>
+          <t>14,18%</t>
         </is>
       </c>
     </row>
@@ -5758,72 +5758,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>299</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>258916</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>246942</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>268365</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>88,47%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>84,38%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>91,7%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>300</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>236329</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>218645</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>249926</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>86,11%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>79,66%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>91,06%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>299</t>
-        </is>
-      </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>263480</t>
+          <t>225870</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>245010</t>
+          <t>216511</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>275822</t>
+          <t>234676</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>86,25%</t>
+          <t>88,41%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>80,2%</t>
+          <t>84,75%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>90,29%</t>
+          <t>91,86%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5833,32 +5833,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>499809</t>
+          <t>484786</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>473531</t>
+          <t>470390</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>519533</t>
+          <t>497460</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>86,18%</t>
+          <t>88,44%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>81,65%</t>
+          <t>85,82%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>89,58%</t>
+          <t>90,76%</t>
         </is>
       </c>
     </row>
@@ -5871,57 +5871,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>342</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>292645</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>292645</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>292645</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>341</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>274458</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>274458</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>274458</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>342</t>
-        </is>
-      </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>305483</t>
+          <t>255478</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>305483</t>
+          <t>255478</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>305483</t>
+          <t>255478</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -5946,17 +5946,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>579941</t>
+          <t>548122</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>579941</t>
+          <t>548122</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>579941</t>
+          <t>548122</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -5988,72 +5988,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>120</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>87640</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>73275</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>105461</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>12,53%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>10,48%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>15,08%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>117</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>89694</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>71831</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>111837</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>13,48%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>10,8%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>16,81%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>120</t>
-        </is>
-      </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>105554</t>
+          <t>76600</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>85913</t>
+          <t>64089</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>128326</t>
+          <t>90782</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>13,88%</t>
+          <t>12,19%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>11,3%</t>
+          <t>10,2%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>16,88%</t>
+          <t>14,44%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6063,32 +6063,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>195248</t>
+          <t>164240</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>168616</t>
+          <t>143231</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>228630</t>
+          <t>185929</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>13,7%</t>
+          <t>12,37%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>11,83%</t>
+          <t>10,79%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>16,04%</t>
+          <t>14,0%</t>
         </is>
       </c>
     </row>
@@ -6101,72 +6101,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>855</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>611616</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>593795</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>625981</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>87,47%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>84,92%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>89,52%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>825</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>575462</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>553319</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>593325</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>86,52%</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>83,19%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>89,2%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>855</t>
-        </is>
-      </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>654768</t>
+          <t>552003</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>631996</t>
+          <t>537821</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>674409</t>
+          <t>564514</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>86,12%</t>
+          <t>87,81%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>83,12%</t>
+          <t>85,56%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>88,7%</t>
+          <t>89,8%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6176,32 +6176,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>1230229</t>
+          <t>1163619</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1196847</t>
+          <t>1141930</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1256861</t>
+          <t>1184628</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>86,3%</t>
+          <t>87,63%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>83,96%</t>
+          <t>86,0%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>88,17%</t>
+          <t>89,21%</t>
         </is>
       </c>
     </row>
@@ -6214,57 +6214,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>975</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>699256</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>699256</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>699256</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>942</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>665156</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>665156</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>665156</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>975</t>
-        </is>
-      </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>760322</t>
+          <t>628603</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>760322</t>
+          <t>628603</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>760322</t>
+          <t>628603</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -6289,17 +6289,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>1425477</t>
+          <t>1327859</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1425477</t>
+          <t>1327859</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1425477</t>
+          <t>1327859</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
